--- a/MSME/Test upload format/MSME_D2.xlsx
+++ b/MSME/Test upload format/MSME_D2.xlsx
@@ -41,7 +41,7 @@
     <t>DisbursementDate</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357192</t>
+    <t>CGMSMGEN2210202600357238</t>
   </si>
   <si>
     <t>Aloan01</t>
@@ -53,7 +53,7 @@
     <t>15-04-2027</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357193</t>
+    <t>CGMSMGEN2210202600357239</t>
   </si>
   <si>
     <t>Aloan02</t>
@@ -62,7 +62,7 @@
     <t>500000000</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357194</t>
+    <t>CGMSMGEN2210202600357240</t>
   </si>
   <si>
     <t>Aloan03</t>
@@ -71,13 +71,13 @@
     <t>200000000</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357195</t>
+    <t>CGMSMGEN2210202600357241</t>
   </si>
   <si>
     <t>Aloan04</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357196</t>
+    <t>CGMSMGEN2210202600357242</t>
   </si>
   <si>
     <t>Aloan05</t>
@@ -86,7 +86,7 @@
     <t>300000000</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357197</t>
+    <t>CGMSMGEN2210202600357243</t>
   </si>
   <si>
     <t>Aloan06</t>
@@ -95,13 +95,13 @@
     <t>40000000</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357198</t>
+    <t>CGMSMGEN2210202600357244</t>
   </si>
   <si>
     <t>Aloan07</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357199</t>
+    <t>CGMSMGEN2210202600357245</t>
   </si>
   <si>
     <t>Aloan08</t>
@@ -110,7 +110,7 @@
     <t>10000000</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357200</t>
+    <t>CGMSMGEN2210202600357246</t>
   </si>
   <si>
     <t>Aloan09</t>
@@ -119,13 +119,13 @@
     <t>50000000</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357201</t>
+    <t>CGMSMGEN2210202600357247</t>
   </si>
   <si>
     <t>Aloan10</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357202</t>
+    <t>CGMSMGEN2210202600357248</t>
   </si>
   <si>
     <t>Aloan11</t>
@@ -134,79 +134,79 @@
     <t>80000000</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357203</t>
+    <t>CGMSMGEN2210202600357249</t>
   </si>
   <si>
     <t>Aloan12</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357204</t>
+    <t>CGMSMGEN2210202600357250</t>
   </si>
   <si>
     <t>Aloan13</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357205</t>
+    <t>CGMSMGEN2210202600357251</t>
   </si>
   <si>
     <t>Aloan14</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357206</t>
+    <t>CGMSMGEN2210202600357252</t>
   </si>
   <si>
     <t>Aloan15</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357207</t>
+    <t>CGMSMGEN2210202600357253</t>
   </si>
   <si>
     <t>Aloan16</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357208</t>
+    <t>CGMSMGEN2210202600357254</t>
   </si>
   <si>
     <t>Aloan17</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357209</t>
+    <t>CGMSMGEN2210202600357255</t>
   </si>
   <si>
     <t>Aloan18</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357210</t>
+    <t>CGMSMGEN2210202600357256</t>
   </si>
   <si>
     <t>Aloan19</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357211</t>
+    <t>CGMSMGEN2210202600357257</t>
   </si>
   <si>
     <t>Aloan20</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357212</t>
+    <t>CGMSMGEN2210202600357258</t>
   </si>
   <si>
     <t>Aloan21</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357213</t>
+    <t>CGMSMGEN2210202600357259</t>
   </si>
   <si>
     <t>Aloan22</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357214</t>
+    <t>CGMSMGEN2210202600357260</t>
   </si>
   <si>
     <t>Aloan23</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357215</t>
+    <t>CGMSMGEN2210202600357261</t>
   </si>
   <si>
     <t>Aloan24</t>
@@ -408,18 +408,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -764,7 +758,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -788,16 +782,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -806,90 +800,90 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -906,7 +900,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1202,10 +1195,10 @@
       <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1216,10 +1209,10 @@
       <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1230,52 +1223,52 @@
       <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:4">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:4">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1286,10 +1279,10 @@
       <c r="B8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1300,10 +1293,10 @@
       <c r="B9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1314,220 +1307,220 @@
       <c r="B10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:4">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:4">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:4">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:4">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:4">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:4">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" ht="15" spans="1:4">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" ht="15" spans="1:4">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:4">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:4">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:4">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:4">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:4">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:4">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:4">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>7</v>
       </c>
     </row>
